--- a/_data/PLCTags_FG_Transport.xlsx
+++ b/_data/PLCTags_FG_Transport.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="Re8c71a4e49774b7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Rdf57104a983c4487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="Ra367c36be2a646e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Rede34bcd7856476e"/>
   </x:sheets>
 </x:workbook>
 </file>
